--- a/Mortalité-décès/Chaleur et mortalité 2025.xlsx
+++ b/Mortalité-décès/Chaleur et mortalité 2025.xlsx
@@ -1,27 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oxfamfrance-my.sharepoint.com/personal/rehl_oxfamfrance_org/Documents/Documents/Santé et climat/Données/Chaleur tue/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{837A60A8-6584-4063-9436-A5CB7BDF6FCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{496C4F6A-8FDF-4954-BD51-935A207891B9}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="8_{837A60A8-6584-4063-9436-A5CB7BDF6FCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4AD1A008-5B3C-4732-BE19-7FC5594786CD}"/>
   <bookViews>
-    <workbookView xWindow="32445" yWindow="1665" windowWidth="21600" windowHeight="11295" xr2:uid="{3147D4C4-7EF5-4BA2-8C7E-5B5D6FC04DBF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3147D4C4-7EF5-4BA2-8C7E-5B5D6FC04DBF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="source" sheetId="2" r:id="rId2"/>
+    <sheet name="Sources" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="204">
   <si>
     <t>DEP_NUM</t>
   </si>
@@ -611,12 +624,6 @@
     <t>Val-d'Oise</t>
   </si>
   <si>
-    <t>972</t>
-  </si>
-  <si>
-    <t>Martinique</t>
-  </si>
-  <si>
     <t>974</t>
   </si>
   <si>
@@ -626,19 +633,19 @@
     <t>Pauvre</t>
   </si>
   <si>
-    <t>Taux de pauvreté (en %) au seuil de 60 % de la médiane du niveau de vie</t>
-  </si>
-  <si>
-    <t>https://www.insee.fr/fr/statistiques/7756729?sommaire=7756859</t>
-  </si>
-  <si>
     <t>Morts_2025</t>
   </si>
   <si>
     <t>https://www.santepubliquefrance.fr/determinants-de-sante/climat/fortes-chaleurs-canicule/documents/bulletin-national/chaleur-et-sante.-bilan-de-l-ete-2025</t>
   </si>
   <si>
-    <t>Interprétation de la carte. Attention, il s'agit à chaque fois de la fourchette basse.</t>
+    <t>Interprétation de la carte en utilisant, pour chaque département, la fourchette basse</t>
+  </si>
+  <si>
+    <t>Taux de pauvreté à 60 %</t>
+  </si>
+  <si>
+    <t>https://www.insee.fr/fr/statistiques/8984752?sommaire=8984758</t>
   </si>
 </sst>
 </file>
@@ -648,7 +655,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="21">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -753,6 +760,24 @@
       <color theme="0"/>
       <name val="Liberation Sans"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Liberation Sans"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -834,7 +859,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
+  <cellStyleXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="8" borderId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
@@ -855,21 +880,27 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="20" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="19" fillId="0" borderId="0" xfId="20" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="20" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="21"/>
   </cellXfs>
-  <cellStyles count="20">
+  <cellStyles count="22">
     <cellStyle name="Accent" xfId="2" xr:uid="{338582FE-5134-4E3E-A028-AB42B21ACDAD}"/>
     <cellStyle name="Accent 1" xfId="3" xr:uid="{4FFBF041-6A41-4945-8F6A-CFF867B8EC4B}"/>
     <cellStyle name="Accent 2" xfId="4" xr:uid="{AEA41EE3-4010-43BF-AF74-45B727AC6201}"/>
@@ -883,8 +914,10 @@
     <cellStyle name="Heading 1" xfId="12" xr:uid="{8964315E-BF52-4249-A621-D172BE1AA431}"/>
     <cellStyle name="Heading 2" xfId="13" xr:uid="{F34868CC-802F-4607-AEFC-6A2D14C15DB4}"/>
     <cellStyle name="Hyperlink" xfId="14" xr:uid="{C3337AFF-AC6F-403C-A880-2B46A394181D}"/>
+    <cellStyle name="Lien hypertexte" xfId="21" builtinId="8"/>
     <cellStyle name="Neutral" xfId="15" xr:uid="{9DE4D510-6A5C-434F-9610-1F35251ED38C}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
+    <cellStyle name="Normal 2" xfId="20" xr:uid="{7CD2BA0D-ADE6-4F1B-B579-145A5074B145}"/>
     <cellStyle name="Note" xfId="1" builtinId="10" customBuiltin="1"/>
     <cellStyle name="Result" xfId="16" xr:uid="{3D429C56-9BCC-4D3E-9E70-EB3E5583B851}"/>
     <cellStyle name="Status" xfId="17" xr:uid="{B11B0C18-616F-4C9E-82BC-18064EA67273}"/>
@@ -902,10 +935,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1225,27 +1254,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AF17438-C72C-4640-AFBF-EE7097F479E4}">
-  <dimension ref="A1:D99"/>
+  <dimension ref="A1:F98"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="4" width="12.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="6" customFormat="1">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:6" s="4" customFormat="1">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="5" t="s">
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1255,11 +1284,13 @@
       <c r="C2">
         <v>2</v>
       </c>
-      <c r="D2" s="2">
-        <v>10.8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="D2" s="7">
+        <v>12.2</v>
+      </c>
+      <c r="E2" s="5"/>
+      <c r="F2" s="7"/>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -1269,11 +1300,13 @@
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="D3" s="2">
-        <v>18.8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="D3" s="7">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="E3" s="5"/>
+      <c r="F3" s="7"/>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -1283,11 +1316,13 @@
       <c r="C4">
         <v>3</v>
       </c>
-      <c r="D4" s="2">
-        <v>16.2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="38.25">
+      <c r="D4" s="7">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="E4" s="5"/>
+      <c r="F4" s="7"/>
+    </row>
+    <row r="5" spans="1:6" ht="38.25">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -1297,11 +1332,13 @@
       <c r="C5">
         <v>4</v>
       </c>
-      <c r="D5" s="2">
-        <v>17.100000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="D5" s="7">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="E5" s="5"/>
+      <c r="F5" s="7"/>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -1311,11 +1348,13 @@
       <c r="C6">
         <v>4</v>
       </c>
-      <c r="D6" s="2">
-        <v>14.7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="25.5">
+      <c r="D6" s="7">
+        <v>14.3</v>
+      </c>
+      <c r="E6" s="5"/>
+      <c r="F6" s="7"/>
+    </row>
+    <row r="7" spans="1:6" ht="25.5">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -1325,11 +1364,13 @@
       <c r="C7">
         <v>4</v>
       </c>
-      <c r="D7" s="2">
-        <v>16.399999999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="D7" s="7">
+        <v>17.7</v>
+      </c>
+      <c r="E7" s="5"/>
+      <c r="F7" s="7"/>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
@@ -1339,11 +1380,13 @@
       <c r="C8">
         <v>4</v>
       </c>
-      <c r="D8" s="2">
-        <v>14.9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="D8" s="7">
+        <v>15.6</v>
+      </c>
+      <c r="E8" s="5"/>
+      <c r="F8" s="7"/>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="1" t="s">
         <v>18</v>
       </c>
@@ -1353,11 +1396,13 @@
       <c r="C9">
         <v>3</v>
       </c>
-      <c r="D9" s="2">
-        <v>19.399999999999999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+      <c r="D9" s="7">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="E9" s="5"/>
+      <c r="F9" s="7"/>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="1" t="s">
         <v>20</v>
       </c>
@@ -1367,11 +1412,13 @@
       <c r="C10">
         <v>4</v>
       </c>
-      <c r="D10" s="3">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+      <c r="D10" s="6">
+        <v>20</v>
+      </c>
+      <c r="E10" s="5"/>
+      <c r="F10" s="6"/>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="1" t="s">
         <v>22</v>
       </c>
@@ -1381,11 +1428,13 @@
       <c r="C11">
         <v>2</v>
       </c>
-      <c r="D11" s="2">
-        <v>16.899999999999999</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+      <c r="D11" s="7">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E11" s="5"/>
+      <c r="F11" s="7"/>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" s="1" t="s">
         <v>24</v>
       </c>
@@ -1395,11 +1444,13 @@
       <c r="C12">
         <v>4</v>
       </c>
-      <c r="D12" s="2">
-        <v>20.8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
+      <c r="D12" s="7">
+        <v>21.2</v>
+      </c>
+      <c r="E12" s="5"/>
+      <c r="F12" s="7"/>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" s="1" t="s">
         <v>26</v>
       </c>
@@ -1409,11 +1460,13 @@
       <c r="C13">
         <v>4</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="7">
         <v>14.5</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" ht="25.5">
+      <c r="E13" s="5"/>
+      <c r="F13" s="7"/>
+    </row>
+    <row r="14" spans="1:6" ht="25.5">
       <c r="A14" s="1" t="s">
         <v>28</v>
       </c>
@@ -1423,11 +1476,13 @@
       <c r="C14">
         <v>4</v>
       </c>
-      <c r="D14" s="2">
-        <v>18.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
+      <c r="D14" s="7">
+        <v>20.3</v>
+      </c>
+      <c r="E14" s="5"/>
+      <c r="F14" s="7"/>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15" s="1" t="s">
         <v>30</v>
       </c>
@@ -1437,11 +1492,13 @@
       <c r="C15">
         <v>1</v>
       </c>
-      <c r="D15" s="2">
-        <v>12.5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
+      <c r="D15" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="E15" s="5"/>
+      <c r="F15" s="7"/>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16" s="1" t="s">
         <v>32</v>
       </c>
@@ -1451,11 +1508,13 @@
       <c r="C16">
         <v>4</v>
       </c>
-      <c r="D16" s="2">
-        <v>14.2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
+      <c r="D16" s="7">
+        <v>13.7</v>
+      </c>
+      <c r="E16" s="5"/>
+      <c r="F16" s="7"/>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
@@ -1465,11 +1524,13 @@
       <c r="C17">
         <v>4</v>
       </c>
-      <c r="D17" s="2">
-        <v>15.1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="25.5">
+      <c r="D17" s="7">
+        <v>15.4</v>
+      </c>
+      <c r="E17" s="5"/>
+      <c r="F17" s="7"/>
+    </row>
+    <row r="18" spans="1:6" ht="25.5">
       <c r="A18" s="1" t="s">
         <v>36</v>
       </c>
@@ -1479,11 +1540,13 @@
       <c r="C18">
         <v>2</v>
       </c>
-      <c r="D18" s="2">
-        <v>12.5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
+      <c r="D18" s="7">
+        <v>13.1</v>
+      </c>
+      <c r="E18" s="5"/>
+      <c r="F18" s="7"/>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" s="1" t="s">
         <v>38</v>
       </c>
@@ -1493,11 +1556,13 @@
       <c r="C19">
         <v>4</v>
       </c>
-      <c r="D19" s="2">
-        <v>14.7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
+      <c r="D19" s="7">
+        <v>15.9</v>
+      </c>
+      <c r="E19" s="5"/>
+      <c r="F19" s="7"/>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" s="1" t="s">
         <v>40</v>
       </c>
@@ -1507,165 +1572,189 @@
       <c r="C20">
         <v>4</v>
       </c>
-      <c r="D20" s="2">
-        <v>13.7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="25.5">
+      <c r="D20" s="7">
+        <v>14.4</v>
+      </c>
+      <c r="E20" s="5"/>
+      <c r="F20" s="7"/>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21">
+        <v>3</v>
+      </c>
+      <c r="D21" s="6">
+        <v>13</v>
+      </c>
+      <c r="E21" s="5"/>
+      <c r="F21" s="6"/>
+    </row>
+    <row r="22" spans="1:6" ht="25.5">
+      <c r="A22" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+      <c r="D22" s="7">
+        <v>12.2</v>
+      </c>
+      <c r="E22" s="5"/>
+      <c r="F22" s="7"/>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C23">
+        <v>4</v>
+      </c>
+      <c r="D23" s="7">
+        <v>19.5</v>
+      </c>
+      <c r="E23" s="5"/>
+      <c r="F23" s="7"/>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C24">
+        <v>4</v>
+      </c>
+      <c r="D24" s="7">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="E24" s="5"/>
+      <c r="F24" s="7"/>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C25">
+        <v>2</v>
+      </c>
+      <c r="D25" s="7">
+        <v>13.4</v>
+      </c>
+      <c r="E25" s="5"/>
+      <c r="F25" s="7"/>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C26">
+        <v>4</v>
+      </c>
+      <c r="D26" s="6">
+        <v>16</v>
+      </c>
+      <c r="E26" s="5"/>
+      <c r="F26" s="6"/>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C27">
+        <v>2</v>
+      </c>
+      <c r="D27" s="7">
+        <v>13.8</v>
+      </c>
+      <c r="E27" s="5"/>
+      <c r="F27" s="7"/>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C28">
+        <v>2</v>
+      </c>
+      <c r="D28" s="7">
+        <v>13.3</v>
+      </c>
+      <c r="E28" s="5"/>
+      <c r="F28" s="7"/>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C29">
+        <v>2</v>
+      </c>
+      <c r="D29" s="7">
+        <v>11.4</v>
+      </c>
+      <c r="E29" s="5"/>
+      <c r="F29" s="7"/>
+    </row>
+    <row r="30" spans="1:6" ht="25.5">
+      <c r="A30" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B30" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C21">
-        <v>2</v>
-      </c>
-      <c r="D21" s="2">
-        <v>15.8</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="1" t="s">
+      <c r="C30">
+        <v>2</v>
+      </c>
+      <c r="D30" s="7">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="E30" s="5"/>
+      <c r="F30" s="7"/>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B31" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C22">
-        <v>4</v>
-      </c>
-      <c r="D22" s="2">
-        <v>20.2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C23">
-        <v>3</v>
-      </c>
-      <c r="D23" s="2">
-        <v>11.8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="25.5">
-      <c r="A24" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C24">
-        <v>2</v>
-      </c>
-      <c r="D24" s="2">
-        <v>11.8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C25">
-        <v>4</v>
-      </c>
-      <c r="D25" s="2">
-        <v>19.2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C26">
-        <v>4</v>
-      </c>
-      <c r="D26" s="2">
-        <v>16.600000000000001</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C27">
-        <v>2</v>
-      </c>
-      <c r="D27" s="2">
-        <v>13.1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C28">
-        <v>4</v>
-      </c>
-      <c r="D28" s="2">
-        <v>14.8</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C29">
-        <v>2</v>
-      </c>
-      <c r="D29" s="2">
-        <v>12.7</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C30">
-        <v>2</v>
-      </c>
-      <c r="D30" s="2">
-        <v>12.1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>63</v>
-      </c>
       <c r="C31">
-        <v>2</v>
-      </c>
-      <c r="D31" s="2">
-        <v>10.8</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
+        <v>4</v>
+      </c>
+      <c r="D31" s="7">
+        <v>21.8</v>
+      </c>
+      <c r="E31" s="5"/>
+      <c r="F31" s="7"/>
+    </row>
+    <row r="32" spans="1:6">
       <c r="A32" s="1" t="s">
         <v>64</v>
       </c>
@@ -1675,11 +1764,13 @@
       <c r="C32">
         <v>4</v>
       </c>
-      <c r="D32" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="25.5">
+      <c r="D32" s="6">
+        <v>21</v>
+      </c>
+      <c r="E32" s="5"/>
+      <c r="F32" s="6"/>
+    </row>
+    <row r="33" spans="1:6" ht="25.5">
       <c r="A33" s="1" t="s">
         <v>66</v>
       </c>
@@ -1689,11 +1780,13 @@
       <c r="C33">
         <v>2</v>
       </c>
-      <c r="D33" s="2">
-        <v>14.3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
+      <c r="D33" s="7">
+        <v>15.9</v>
+      </c>
+      <c r="E33" s="5"/>
+      <c r="F33" s="7"/>
+    </row>
+    <row r="34" spans="1:6">
       <c r="A34" s="1" t="s">
         <v>68</v>
       </c>
@@ -1703,11 +1796,13 @@
       <c r="C34">
         <v>3</v>
       </c>
-      <c r="D34" s="2">
-        <v>15.3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
+      <c r="D34" s="7">
+        <v>15.6</v>
+      </c>
+      <c r="E34" s="5"/>
+      <c r="F34" s="7"/>
+    </row>
+    <row r="35" spans="1:6">
       <c r="A35" s="1" t="s">
         <v>70</v>
       </c>
@@ -1717,11 +1812,13 @@
       <c r="C35">
         <v>3</v>
       </c>
-      <c r="D35" s="2">
-        <v>12.8</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
+      <c r="D35" s="7">
+        <v>14.2</v>
+      </c>
+      <c r="E35" s="5"/>
+      <c r="F35" s="7"/>
+    </row>
+    <row r="36" spans="1:6">
       <c r="A36" s="1" t="s">
         <v>72</v>
       </c>
@@ -1731,11 +1828,13 @@
       <c r="C36">
         <v>4</v>
       </c>
-      <c r="D36" s="2">
-        <v>19.399999999999999</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
+      <c r="D36" s="6">
+        <v>21</v>
+      </c>
+      <c r="E36" s="5"/>
+      <c r="F36" s="6"/>
+    </row>
+    <row r="37" spans="1:6">
       <c r="A37" s="1" t="s">
         <v>74</v>
       </c>
@@ -1745,11 +1844,13 @@
       <c r="C37">
         <v>4</v>
       </c>
-      <c r="D37" s="2">
-        <v>10.8</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
+      <c r="D37" s="7">
+        <v>11.7</v>
+      </c>
+      <c r="E37" s="5"/>
+      <c r="F37" s="7"/>
+    </row>
+    <row r="38" spans="1:6">
       <c r="A38" s="1" t="s">
         <v>76</v>
       </c>
@@ -1759,11 +1860,13 @@
       <c r="C38">
         <v>2</v>
       </c>
-      <c r="D38" s="2">
-        <v>15.4</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
+      <c r="D38" s="7">
+        <v>15.8</v>
+      </c>
+      <c r="E38" s="5"/>
+      <c r="F38" s="7"/>
+    </row>
+    <row r="39" spans="1:6">
       <c r="A39" s="1" t="s">
         <v>78</v>
       </c>
@@ -1773,11 +1876,13 @@
       <c r="C39">
         <v>1</v>
       </c>
-      <c r="D39" s="2">
-        <v>12.8</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
+      <c r="D39" s="7">
+        <v>14.1</v>
+      </c>
+      <c r="E39" s="5"/>
+      <c r="F39" s="7"/>
+    </row>
+    <row r="40" spans="1:6">
       <c r="A40" s="1" t="s">
         <v>80</v>
       </c>
@@ -1787,11 +1892,13 @@
       <c r="C40">
         <v>4</v>
       </c>
-      <c r="D40" s="2">
-        <v>11.8</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
+      <c r="D40" s="6">
+        <v>13</v>
+      </c>
+      <c r="E40" s="5"/>
+      <c r="F40" s="6"/>
+    </row>
+    <row r="41" spans="1:6">
       <c r="A41" s="1" t="s">
         <v>82</v>
       </c>
@@ -1801,11 +1908,13 @@
       <c r="C41">
         <v>3</v>
       </c>
-      <c r="D41" s="2">
-        <v>11.8</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
+      <c r="D41" s="7">
+        <v>12.3</v>
+      </c>
+      <c r="E41" s="5"/>
+      <c r="F41" s="7"/>
+    </row>
+    <row r="42" spans="1:6">
       <c r="A42" s="1" t="s">
         <v>84</v>
       </c>
@@ -1815,11 +1924,13 @@
       <c r="C42">
         <v>2</v>
       </c>
-      <c r="D42" s="2">
-        <v>11.7</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4">
+      <c r="D42" s="7">
+        <v>12.1</v>
+      </c>
+      <c r="E42" s="5"/>
+      <c r="F42" s="7"/>
+    </row>
+    <row r="43" spans="1:6">
       <c r="A43" s="1" t="s">
         <v>86</v>
       </c>
@@ -1829,11 +1940,13 @@
       <c r="C43">
         <v>3</v>
       </c>
-      <c r="D43" s="2">
-        <v>13.2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4">
+      <c r="D43" s="6">
+        <v>14</v>
+      </c>
+      <c r="E43" s="5"/>
+      <c r="F43" s="6"/>
+    </row>
+    <row r="44" spans="1:6">
       <c r="A44" s="1" t="s">
         <v>88</v>
       </c>
@@ -1843,11 +1956,13 @@
       <c r="C44">
         <v>4</v>
       </c>
-      <c r="D44" s="2">
-        <v>15.8</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
+      <c r="D44" s="7">
+        <v>16.8</v>
+      </c>
+      <c r="E44" s="5"/>
+      <c r="F44" s="7"/>
+    </row>
+    <row r="45" spans="1:6">
       <c r="A45" s="1" t="s">
         <v>90</v>
       </c>
@@ -1857,11 +1972,13 @@
       <c r="C45">
         <v>4</v>
       </c>
-      <c r="D45" s="2">
-        <v>12.3</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" ht="25.5">
+      <c r="D45" s="7">
+        <v>12.4</v>
+      </c>
+      <c r="E45" s="5"/>
+      <c r="F45" s="7"/>
+    </row>
+    <row r="46" spans="1:6" ht="25.5">
       <c r="A46" s="1" t="s">
         <v>92</v>
       </c>
@@ -1871,11 +1988,13 @@
       <c r="C46">
         <v>3</v>
       </c>
-      <c r="D46" s="2">
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
+      <c r="D46" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="E46" s="5"/>
+      <c r="F46" s="7"/>
+    </row>
+    <row r="47" spans="1:6">
       <c r="A47" s="1" t="s">
         <v>94</v>
       </c>
@@ -1885,11 +2004,13 @@
       <c r="C47">
         <v>2</v>
       </c>
-      <c r="D47" s="2">
-        <v>13.9</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
+      <c r="D47" s="6">
+        <v>15</v>
+      </c>
+      <c r="E47" s="5"/>
+      <c r="F47" s="6"/>
+    </row>
+    <row r="48" spans="1:6">
       <c r="A48" s="1" t="s">
         <v>96</v>
       </c>
@@ -1899,11 +2020,13 @@
       <c r="C48">
         <v>4</v>
       </c>
-      <c r="D48" s="2">
-        <v>15.3</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" ht="25.5">
+      <c r="D48" s="7">
+        <v>15.8</v>
+      </c>
+      <c r="E48" s="5"/>
+      <c r="F48" s="7"/>
+    </row>
+    <row r="49" spans="1:6" ht="25.5">
       <c r="A49" s="1" t="s">
         <v>98</v>
       </c>
@@ -1913,11 +2036,13 @@
       <c r="C49">
         <v>4</v>
       </c>
-      <c r="D49" s="2">
-        <v>17.7</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4">
+      <c r="D49" s="7">
+        <v>18.5</v>
+      </c>
+      <c r="E49" s="5"/>
+      <c r="F49" s="7"/>
+    </row>
+    <row r="50" spans="1:6">
       <c r="A50" s="1" t="s">
         <v>100</v>
       </c>
@@ -1927,11 +2052,13 @@
       <c r="C50">
         <v>4</v>
       </c>
-      <c r="D50" s="2">
-        <v>15.5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" ht="25.5">
+      <c r="D50" s="7">
+        <v>15.3</v>
+      </c>
+      <c r="E50" s="5"/>
+      <c r="F50" s="7"/>
+    </row>
+    <row r="51" spans="1:6" ht="25.5">
       <c r="A51" s="1" t="s">
         <v>102</v>
       </c>
@@ -1941,11 +2068,13 @@
       <c r="C51">
         <v>3</v>
       </c>
-      <c r="D51" s="2">
-        <v>11.5</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4">
+      <c r="D51" s="7">
+        <v>11.8</v>
+      </c>
+      <c r="E51" s="5"/>
+      <c r="F51" s="7"/>
+    </row>
+    <row r="52" spans="1:6">
       <c r="A52" s="1" t="s">
         <v>104</v>
       </c>
@@ -1955,11 +2084,13 @@
       <c r="C52">
         <v>2</v>
       </c>
-      <c r="D52" s="2">
-        <v>11.7</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4">
+      <c r="D52" s="6">
+        <v>12</v>
+      </c>
+      <c r="E52" s="5"/>
+      <c r="F52" s="6"/>
+    </row>
+    <row r="53" spans="1:6">
       <c r="A53" s="1" t="s">
         <v>106</v>
       </c>
@@ -1969,11 +2100,13 @@
       <c r="C53">
         <v>3</v>
       </c>
-      <c r="D53" s="3">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4">
+      <c r="D53" s="7">
+        <v>15.8</v>
+      </c>
+      <c r="E53" s="5"/>
+      <c r="F53" s="7"/>
+    </row>
+    <row r="54" spans="1:6">
       <c r="A54" s="1" t="s">
         <v>108</v>
       </c>
@@ -1983,11 +2116,13 @@
       <c r="C54">
         <v>3</v>
       </c>
-      <c r="D54" s="2">
-        <v>15.3</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4">
+      <c r="D54" s="6">
+        <v>16</v>
+      </c>
+      <c r="E54" s="5"/>
+      <c r="F54" s="6"/>
+    </row>
+    <row r="55" spans="1:6">
       <c r="A55" s="1" t="s">
         <v>110</v>
       </c>
@@ -1997,11 +2132,13 @@
       <c r="C55">
         <v>2</v>
       </c>
-      <c r="D55" s="2">
-        <v>11.5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" ht="25.5">
+      <c r="D55" s="7">
+        <v>11.6</v>
+      </c>
+      <c r="E55" s="5"/>
+      <c r="F55" s="7"/>
+    </row>
+    <row r="56" spans="1:6" ht="25.5">
       <c r="A56" s="1" t="s">
         <v>112</v>
       </c>
@@ -2011,11 +2148,13 @@
       <c r="C56">
         <v>2</v>
       </c>
-      <c r="D56" s="2">
-        <v>15.3</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4">
+      <c r="D56" s="7">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="E56" s="5"/>
+      <c r="F56" s="7"/>
+    </row>
+    <row r="57" spans="1:6">
       <c r="A57" s="1" t="s">
         <v>114</v>
       </c>
@@ -2025,11 +2164,13 @@
       <c r="C57">
         <v>2</v>
       </c>
-      <c r="D57" s="2">
-        <v>14.8</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4">
+      <c r="D57" s="6">
+        <v>15</v>
+      </c>
+      <c r="E57" s="5"/>
+      <c r="F57" s="6"/>
+    </row>
+    <row r="58" spans="1:6">
       <c r="A58" s="1" t="s">
         <v>116</v>
       </c>
@@ -2039,11 +2180,13 @@
       <c r="C58">
         <v>2</v>
       </c>
-      <c r="D58" s="2">
-        <v>11.1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4">
+      <c r="D58" s="7">
+        <v>11.3</v>
+      </c>
+      <c r="E58" s="5"/>
+      <c r="F58" s="7"/>
+    </row>
+    <row r="59" spans="1:6">
       <c r="A59" s="1" t="s">
         <v>118</v>
       </c>
@@ -2053,11 +2196,13 @@
       <c r="C59">
         <v>2</v>
       </c>
-      <c r="D59" s="2">
-        <v>15.9</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4">
+      <c r="D59" s="7">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="E59" s="5"/>
+      <c r="F59" s="7"/>
+    </row>
+    <row r="60" spans="1:6">
       <c r="A60" s="1" t="s">
         <v>120</v>
       </c>
@@ -2067,11 +2212,13 @@
       <c r="C60">
         <v>3</v>
       </c>
-      <c r="D60" s="2">
-        <v>16.100000000000001</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4">
+      <c r="D60" s="7">
+        <v>17.3</v>
+      </c>
+      <c r="E60" s="5"/>
+      <c r="F60" s="7"/>
+    </row>
+    <row r="61" spans="1:6">
       <c r="A61" s="1" t="s">
         <v>122</v>
       </c>
@@ -2081,11 +2228,13 @@
       <c r="C61">
         <v>3</v>
       </c>
-      <c r="D61" s="2">
-        <v>19.5</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4">
+      <c r="D61" s="7">
+        <v>20.7</v>
+      </c>
+      <c r="E61" s="5"/>
+      <c r="F61" s="7"/>
+    </row>
+    <row r="62" spans="1:6">
       <c r="A62" s="1" t="s">
         <v>124</v>
       </c>
@@ -2095,11 +2244,13 @@
       <c r="C62">
         <v>2</v>
       </c>
-      <c r="D62" s="2">
-        <v>13.4</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4">
+      <c r="D62" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="E62" s="5"/>
+      <c r="F62" s="7"/>
+    </row>
+    <row r="63" spans="1:6">
       <c r="A63" s="1" t="s">
         <v>126</v>
       </c>
@@ -2109,11 +2260,13 @@
       <c r="C63">
         <v>3</v>
       </c>
-      <c r="D63" s="2">
-        <v>15.6</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" ht="25.5">
+      <c r="D63" s="7">
+        <v>16.3</v>
+      </c>
+      <c r="E63" s="5"/>
+      <c r="F63" s="7"/>
+    </row>
+    <row r="64" spans="1:6" ht="25.5">
       <c r="A64" s="1" t="s">
         <v>128</v>
       </c>
@@ -2123,11 +2276,13 @@
       <c r="C64">
         <v>2</v>
       </c>
-      <c r="D64" s="2">
-        <v>18.399999999999999</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" ht="25.5">
+      <c r="D64" s="7">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="E64" s="5"/>
+      <c r="F64" s="7"/>
+    </row>
+    <row r="65" spans="1:6" ht="25.5">
       <c r="A65" s="1" t="s">
         <v>130</v>
       </c>
@@ -2137,11 +2292,13 @@
       <c r="C65">
         <v>3</v>
       </c>
-      <c r="D65" s="2">
-        <v>13.9</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" ht="25.5">
+      <c r="D65" s="7">
+        <v>14.8</v>
+      </c>
+      <c r="E65" s="5"/>
+      <c r="F65" s="7"/>
+    </row>
+    <row r="66" spans="1:6" ht="25.5">
       <c r="A66" s="1" t="s">
         <v>132</v>
       </c>
@@ -2151,11 +2308,13 @@
       <c r="C66">
         <v>3</v>
       </c>
-      <c r="D66" s="2">
-        <v>12.6</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" ht="25.5">
+      <c r="D66" s="7">
+        <v>13.3</v>
+      </c>
+      <c r="E66" s="5"/>
+      <c r="F66" s="7"/>
+    </row>
+    <row r="67" spans="1:6" ht="25.5">
       <c r="A67" s="1" t="s">
         <v>134</v>
       </c>
@@ -2165,11 +2324,13 @@
       <c r="C67">
         <v>4</v>
       </c>
-      <c r="D67" s="3">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" ht="25.5">
+      <c r="D67" s="7">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="E67" s="5"/>
+      <c r="F67" s="7"/>
+    </row>
+    <row r="68" spans="1:6" ht="25.5">
       <c r="A68" s="1" t="s">
         <v>136</v>
       </c>
@@ -2179,11 +2340,13 @@
       <c r="C68">
         <v>4</v>
       </c>
-      <c r="D68" s="2">
-        <v>21.2</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4">
+      <c r="D68" s="7">
+        <v>22.4</v>
+      </c>
+      <c r="E68" s="5"/>
+      <c r="F68" s="7"/>
+    </row>
+    <row r="69" spans="1:6">
       <c r="A69" s="1" t="s">
         <v>138</v>
       </c>
@@ -2193,11 +2356,13 @@
       <c r="C69">
         <v>3</v>
       </c>
-      <c r="D69" s="2">
-        <v>13.5</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4">
+      <c r="D69" s="6">
+        <v>15</v>
+      </c>
+      <c r="E69" s="5"/>
+      <c r="F69" s="6"/>
+    </row>
+    <row r="70" spans="1:6">
       <c r="A70" s="1" t="s">
         <v>140</v>
       </c>
@@ -2207,11 +2372,13 @@
       <c r="C70">
         <v>3</v>
       </c>
-      <c r="D70" s="2">
-        <v>13.7</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4">
+      <c r="D70" s="7">
+        <v>14.1</v>
+      </c>
+      <c r="E70" s="5"/>
+      <c r="F70" s="7"/>
+    </row>
+    <row r="71" spans="1:6">
       <c r="A71" s="1" t="s">
         <v>142</v>
       </c>
@@ -2221,11 +2388,13 @@
       <c r="C71">
         <v>1</v>
       </c>
-      <c r="D71" s="2">
-        <v>14.8</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4">
+      <c r="D71" s="7">
+        <v>16.3</v>
+      </c>
+      <c r="E71" s="5"/>
+      <c r="F71" s="7"/>
+    </row>
+    <row r="72" spans="1:6">
       <c r="A72" s="1" t="s">
         <v>144</v>
       </c>
@@ -2235,11 +2404,13 @@
       <c r="C72">
         <v>3</v>
       </c>
-      <c r="D72" s="2">
-        <v>13.6</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" ht="25.5">
+      <c r="D72" s="7">
+        <v>13.8</v>
+      </c>
+      <c r="E72" s="5"/>
+      <c r="F72" s="7"/>
+    </row>
+    <row r="73" spans="1:6" ht="25.5">
       <c r="A73" s="1" t="s">
         <v>146</v>
       </c>
@@ -2249,11 +2420,13 @@
       <c r="C73">
         <v>2</v>
       </c>
-      <c r="D73" s="2">
-        <v>13.3</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4">
+      <c r="D73" s="7">
+        <v>14.1</v>
+      </c>
+      <c r="E73" s="5"/>
+      <c r="F73" s="7"/>
+    </row>
+    <row r="74" spans="1:6">
       <c r="A74" s="1" t="s">
         <v>148</v>
       </c>
@@ -2263,11 +2436,13 @@
       <c r="C74">
         <v>3</v>
       </c>
-      <c r="D74" s="2">
-        <v>13.5</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4">
+      <c r="D74" s="7">
+        <v>14.1</v>
+      </c>
+      <c r="E74" s="5"/>
+      <c r="F74" s="7"/>
+    </row>
+    <row r="75" spans="1:6">
       <c r="A75" s="1" t="s">
         <v>150</v>
       </c>
@@ -2277,11 +2452,13 @@
       <c r="C75">
         <v>4</v>
       </c>
-      <c r="D75" s="2">
-        <v>11.2</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4">
+      <c r="D75" s="7">
+        <v>11.1</v>
+      </c>
+      <c r="E75" s="5"/>
+      <c r="F75" s="7"/>
+    </row>
+    <row r="76" spans="1:6">
       <c r="A76" s="1" t="s">
         <v>152</v>
       </c>
@@ -2291,11 +2468,13 @@
       <c r="C76">
         <v>4</v>
       </c>
-      <c r="D76" s="2">
-        <v>9.5</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4">
+      <c r="D76" s="7">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="E76" s="5"/>
+      <c r="F76" s="7"/>
+    </row>
+    <row r="77" spans="1:6">
       <c r="A77" s="1" t="s">
         <v>154</v>
       </c>
@@ -2305,11 +2484,13 @@
       <c r="C77">
         <v>2</v>
       </c>
-      <c r="D77" s="2">
-        <v>15.6</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" ht="25.5">
+      <c r="D77" s="7">
+        <v>16.8</v>
+      </c>
+      <c r="E77" s="5"/>
+      <c r="F77" s="7"/>
+    </row>
+    <row r="78" spans="1:6" ht="25.5">
       <c r="A78" s="1" t="s">
         <v>156</v>
       </c>
@@ -2319,11 +2500,13 @@
       <c r="C78">
         <v>2</v>
       </c>
-      <c r="D78" s="2">
-        <v>15.4</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" ht="25.5">
+      <c r="D78" s="7">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="E78" s="5"/>
+      <c r="F78" s="7"/>
+    </row>
+    <row r="79" spans="1:6" ht="25.5">
       <c r="A79" s="1" t="s">
         <v>158</v>
       </c>
@@ -2333,11 +2516,13 @@
       <c r="C79">
         <v>2</v>
       </c>
-      <c r="D79" s="2">
-        <v>12.4</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4">
+      <c r="D79" s="7">
+        <v>13.6</v>
+      </c>
+      <c r="E79" s="5"/>
+      <c r="F79" s="7"/>
+    </row>
+    <row r="80" spans="1:6">
       <c r="A80" s="1" t="s">
         <v>160</v>
       </c>
@@ -2347,11 +2532,13 @@
       <c r="C80">
         <v>2</v>
       </c>
-      <c r="D80" s="2">
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4">
+      <c r="D80" s="7">
+        <v>11.6</v>
+      </c>
+      <c r="E80" s="5"/>
+      <c r="F80" s="7"/>
+    </row>
+    <row r="81" spans="1:6">
       <c r="A81" s="1" t="s">
         <v>162</v>
       </c>
@@ -2361,11 +2548,13 @@
       <c r="C81">
         <v>2</v>
       </c>
-      <c r="D81" s="2">
-        <v>12.4</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4">
+      <c r="D81" s="7">
+        <v>12.7</v>
+      </c>
+      <c r="E81" s="5"/>
+      <c r="F81" s="7"/>
+    </row>
+    <row r="82" spans="1:6">
       <c r="A82" s="1" t="s">
         <v>164</v>
       </c>
@@ -2375,11 +2564,13 @@
       <c r="C82">
         <v>2</v>
       </c>
-      <c r="D82" s="2">
-        <v>16.399999999999999</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4">
+      <c r="D82" s="7">
+        <v>17.3</v>
+      </c>
+      <c r="E82" s="5"/>
+      <c r="F82" s="7"/>
+    </row>
+    <row r="83" spans="1:6">
       <c r="A83" s="1" t="s">
         <v>166</v>
       </c>
@@ -2389,11 +2580,13 @@
       <c r="C83">
         <v>3</v>
       </c>
-      <c r="D83" s="2">
-        <v>15.7</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" ht="25.5">
+      <c r="D83" s="7">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="E83" s="5"/>
+      <c r="F83" s="7"/>
+    </row>
+    <row r="84" spans="1:6" ht="25.5">
       <c r="A84" s="1" t="s">
         <v>168</v>
       </c>
@@ -2403,11 +2596,13 @@
       <c r="C84">
         <v>4</v>
       </c>
-      <c r="D84" s="2">
-        <v>16.7</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4">
+      <c r="D84" s="6">
+        <v>17</v>
+      </c>
+      <c r="E84" s="5"/>
+      <c r="F84" s="6"/>
+    </row>
+    <row r="85" spans="1:6">
       <c r="A85" s="1" t="s">
         <v>170</v>
       </c>
@@ -2417,11 +2612,13 @@
       <c r="C85">
         <v>4</v>
       </c>
-      <c r="D85" s="2">
-        <v>15.6</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4">
+      <c r="D85" s="7">
+        <v>16.8</v>
+      </c>
+      <c r="E85" s="5"/>
+      <c r="F85" s="7"/>
+    </row>
+    <row r="86" spans="1:6">
       <c r="A86" s="1" t="s">
         <v>172</v>
       </c>
@@ -2431,11 +2628,13 @@
       <c r="C86">
         <v>4</v>
       </c>
-      <c r="D86" s="2">
-        <v>19.899999999999999</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4">
+      <c r="D86" s="7">
+        <v>21.4</v>
+      </c>
+      <c r="E86" s="5"/>
+      <c r="F86" s="7"/>
+    </row>
+    <row r="87" spans="1:6">
       <c r="A87" s="1" t="s">
         <v>174</v>
       </c>
@@ -2445,11 +2644,13 @@
       <c r="C87">
         <v>3</v>
       </c>
-      <c r="D87" s="2">
-        <v>9.1</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4">
+      <c r="D87" s="7">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="E87" s="5"/>
+      <c r="F87" s="7"/>
+    </row>
+    <row r="88" spans="1:6">
       <c r="A88" s="1" t="s">
         <v>176</v>
       </c>
@@ -2459,11 +2660,13 @@
       <c r="C88">
         <v>4</v>
       </c>
-      <c r="D88" s="2">
-        <v>14.7</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4">
+      <c r="D88" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="E88" s="5"/>
+      <c r="F88" s="7"/>
+    </row>
+    <row r="89" spans="1:6">
       <c r="A89" s="1" t="s">
         <v>178</v>
       </c>
@@ -2473,11 +2676,13 @@
       <c r="C89">
         <v>4</v>
       </c>
-      <c r="D89" s="2">
-        <v>16.100000000000001</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4">
+      <c r="D89" s="7">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="E89" s="5"/>
+      <c r="F89" s="7"/>
+    </row>
+    <row r="90" spans="1:6">
       <c r="A90" s="1" t="s">
         <v>180</v>
       </c>
@@ -2487,11 +2692,13 @@
       <c r="C90">
         <v>2</v>
       </c>
-      <c r="D90" s="2">
-        <v>15.3</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4">
+      <c r="D90" s="7">
+        <v>15.8</v>
+      </c>
+      <c r="E90" s="5"/>
+      <c r="F90" s="7"/>
+    </row>
+    <row r="91" spans="1:6">
       <c r="A91" s="1" t="s">
         <v>182</v>
       </c>
@@ -2501,11 +2708,13 @@
       <c r="C91">
         <v>3</v>
       </c>
-      <c r="D91" s="2">
-        <v>14.9</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" ht="25.5">
+      <c r="D91" s="6">
+        <v>16</v>
+      </c>
+      <c r="E91" s="5"/>
+      <c r="F91" s="6"/>
+    </row>
+    <row r="92" spans="1:6" ht="25.5">
       <c r="A92" s="1" t="s">
         <v>184</v>
       </c>
@@ -2515,11 +2724,13 @@
       <c r="C92">
         <v>3</v>
       </c>
-      <c r="D92" s="2">
-        <v>16.3</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4">
+      <c r="D92" s="7">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="E92" s="5"/>
+      <c r="F92" s="7"/>
+    </row>
+    <row r="93" spans="1:6">
       <c r="A93" s="1" t="s">
         <v>186</v>
       </c>
@@ -2529,11 +2740,13 @@
       <c r="C93">
         <v>2</v>
       </c>
-      <c r="D93" s="2">
-        <v>13.9</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" ht="25.5">
+      <c r="D93" s="7">
+        <v>15.4</v>
+      </c>
+      <c r="E93" s="5"/>
+      <c r="F93" s="7"/>
+    </row>
+    <row r="94" spans="1:6" ht="25.5">
       <c r="A94" s="1" t="s">
         <v>188</v>
       </c>
@@ -2543,11 +2756,13 @@
       <c r="C94">
         <v>2</v>
       </c>
-      <c r="D94" s="2">
-        <v>12.4</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" ht="25.5">
+      <c r="D94" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="E94" s="5"/>
+      <c r="F94" s="7"/>
+    </row>
+    <row r="95" spans="1:6" ht="25.5">
       <c r="A95" s="1" t="s">
         <v>190</v>
       </c>
@@ -2557,11 +2772,13 @@
       <c r="C95">
         <v>3</v>
       </c>
-      <c r="D95" s="2">
-        <v>28.4</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4">
+      <c r="D95" s="7">
+        <v>29.5</v>
+      </c>
+      <c r="E95" s="5"/>
+      <c r="F95" s="7"/>
+    </row>
+    <row r="96" spans="1:6">
       <c r="A96" s="1" t="s">
         <v>192</v>
       </c>
@@ -2571,11 +2788,13 @@
       <c r="C96">
         <v>2</v>
       </c>
-      <c r="D96" s="2">
-        <v>17.2</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4">
+      <c r="D96" s="7">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="E96" s="5"/>
+      <c r="F96" s="7"/>
+    </row>
+    <row r="97" spans="1:6">
       <c r="A97" s="1" t="s">
         <v>194</v>
       </c>
@@ -2585,33 +2804,27 @@
       <c r="C97">
         <v>3</v>
       </c>
-      <c r="D97" s="2">
-        <v>17.7</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4">
+      <c r="D97" s="7">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="E97" s="5"/>
+      <c r="F97" s="7"/>
+    </row>
+    <row r="98" spans="1:6">
       <c r="A98" s="1" t="s">
         <v>196</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="D98" s="2">
-        <v>26.8</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4">
-      <c r="A99" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="D99" s="2">
-        <v>36.1</v>
+      <c r="D98" s="7">
+        <v>36.4</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D98">
+    <sortCondition descending="1" ref="D1:D98"/>
+  </sortState>
   <pageMargins left="0" right="0" top="0.39370078740157483" bottom="0.39370078740157483" header="0" footer="0"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;A</oddHeader>
@@ -2628,29 +2841,33 @@
     <col min="1" max="3" width="12.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" ht="89.25">
+    <row r="2" spans="1:3" ht="38.25">
       <c r="A2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="C2" t="s">
         <v>202</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B3" t="s">
-        <v>205</v>
-      </c>
-      <c r="C3" t="s">
-        <v>204</v>
+        <v>201</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>200</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{013D3148-E2C3-4E98-BA21-9792C4002001}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{421825CE-234D-4065-801E-9E132F48E36B}"/>
+  </hyperlinks>
   <pageMargins left="0" right="0" top="0.39370078740157483" bottom="0.39370078740157483" header="0" footer="0"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;A</oddHeader>
